--- a/artfynd/A 3433-2022 artfynd.xlsx
+++ b/artfynd/A 3433-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 3433-2022 artfynd.xlsx
+++ b/artfynd/A 3433-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY18"/>
+  <dimension ref="A1:AY19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>107018640</v>
+        <v>107018840</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -714,14 +709,14 @@
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Stor-Gröningen S, Jmt</t>
+          <t>Stor-Gröningen SV, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>452821.8708891979</v>
+        <v>453061</v>
       </c>
       <c r="R2" t="n">
-        <v>7030895.480273973</v>
+        <v>7031683</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -751,19 +746,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -791,47 +776,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>107018554</v>
+        <v>107018473</v>
       </c>
       <c r="B3" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -839,10 +814,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>453129.4653065144</v>
+        <v>453257</v>
       </c>
       <c r="R3" t="n">
-        <v>7031183.162436061</v>
+        <v>7031210</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,32 +847,18 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack från fjolåret sannolikt.</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -919,16 +880,11 @@
         <v>107018482</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -959,10 +915,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>453168.167309895</v>
+        <v>453168</v>
       </c>
       <c r="R4" t="n">
-        <v>7031190.662342679</v>
+        <v>7031190</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -992,19 +948,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1035,16 +981,11 @@
         <v>107018568</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1075,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>452979.8598992293</v>
+        <v>452980</v>
       </c>
       <c r="R5" t="n">
-        <v>7030988.168575387</v>
+        <v>7030988</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1108,19 +1049,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1151,16 +1082,11 @@
         <v>107018611</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1191,10 +1117,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>452832.4872173597</v>
+        <v>452833</v>
       </c>
       <c r="R6" t="n">
-        <v>7030854.538844419</v>
+        <v>7030854</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1224,19 +1150,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1264,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>107018496</v>
+        <v>107018698</v>
       </c>
       <c r="B7" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>228579</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1307,10 +1218,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>453168.167309895</v>
+        <v>452822</v>
       </c>
       <c r="R7" t="n">
-        <v>7031190.662342679</v>
+        <v>7030903</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1340,19 +1251,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1380,19 +1281,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>107018698</v>
+        <v>107018719</v>
       </c>
       <c r="B8" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1423,10 +1319,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>452821.989787114</v>
+        <v>452861</v>
       </c>
       <c r="R8" t="n">
-        <v>7030903.545812493</v>
+        <v>7030938</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1456,19 +1352,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1499,12 +1385,7 @@
         <v>107018462</v>
       </c>
       <c r="B9" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1539,10 +1420,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>453282.0093259781</v>
+        <v>453282</v>
       </c>
       <c r="R9" t="n">
-        <v>7031211.853369943</v>
+        <v>7031212</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1572,19 +1453,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1612,15 +1483,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>107018586</v>
+        <v>107018493</v>
       </c>
       <c r="B10" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1628,31 +1494,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6440</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1660,10 +1521,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>453010.9121135077</v>
+        <v>453168</v>
       </c>
       <c r="R10" t="n">
-        <v>7030963.51123431</v>
+        <v>7031190</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1693,32 +1554,18 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1737,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>107018458</v>
+        <v>107018742</v>
       </c>
       <c r="B11" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1753,31 +1595,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1785,10 +1622,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>453282.0093259781</v>
+        <v>452870</v>
       </c>
       <c r="R11" t="n">
-        <v>7031211.853369943</v>
+        <v>7030944</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1818,24 +1655,14 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På kolad ved på gammal tallstubbe.</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1844,6 +1671,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1862,15 +1690,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>107018710</v>
+        <v>107018640</v>
       </c>
       <c r="B12" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1905,10 +1728,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452823.9770339403</v>
+        <v>452822</v>
       </c>
       <c r="R12" t="n">
-        <v>7030977.465742581</v>
+        <v>7030895</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1938,19 +1761,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1978,15 +1791,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>107018473</v>
+        <v>107018710</v>
       </c>
       <c r="B13" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1994,21 +1802,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -2021,10 +1829,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>453256.8458411658</v>
+        <v>452824</v>
       </c>
       <c r="R13" t="n">
-        <v>7031209.532018998</v>
+        <v>7030977</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2054,19 +1862,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2094,37 +1892,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>107018493</v>
+        <v>107018643</v>
       </c>
       <c r="B14" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6440</v>
+        <v>6463</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2137,10 +1930,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>453168.167309895</v>
+        <v>452822</v>
       </c>
       <c r="R14" t="n">
-        <v>7031190.662342679</v>
+        <v>7030895</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2170,19 +1963,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2210,15 +1993,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>107018742</v>
+        <v>107018458</v>
       </c>
       <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2226,26 +2004,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
       <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2253,10 +2036,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452870.1580372934</v>
+        <v>453282</v>
       </c>
       <c r="R15" t="n">
-        <v>7030944.068597839</v>
+        <v>7031212</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2286,24 +2069,14 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AC15" t="inlineStr">
         <is>
-          <t>På kolad ved på gammal tallstubbe.</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2312,7 +2085,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2331,15 +2103,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>107018464</v>
+        <v>107018554</v>
       </c>
       <c r="B16" t="n">
-        <v>76490</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2347,26 +2114,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>228579</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Liten svartspik</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Chaenothecopsis nana</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2374,10 +2146,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>453282.0093259781</v>
+        <v>453129</v>
       </c>
       <c r="R16" t="n">
-        <v>7031211.853369943</v>
+        <v>7031183</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2407,19 +2179,14 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Ringhack från fjolåret sannolikt.</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2428,7 +2195,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2447,42 +2213,42 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>107018643</v>
+        <v>107018586</v>
       </c>
       <c r="B17" t="n">
-        <v>78602</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
       <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2490,10 +2256,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452821.8708891979</v>
+        <v>453011</v>
       </c>
       <c r="R17" t="n">
-        <v>7030895.480273973</v>
+        <v>7030964</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2523,19 +2289,14 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2544,7 +2305,6 @@
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2563,15 +2323,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>107018719</v>
+        <v>107018464</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78339</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,21 +2334,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6425</v>
+        <v>228579</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Liten svartspik</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Chaenothecopsis nana</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2606,10 +2361,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452861.5406331714</v>
+        <v>453282</v>
       </c>
       <c r="R18" t="n">
-        <v>7030937.921038928</v>
+        <v>7031212</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2639,19 +2394,9 @@
           <t>2023-02-25</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2023-02-25</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2676,6 +2421,107 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>107018496</v>
+      </c>
+      <c r="B19" t="n">
+        <v>78339</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>228579</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Liten svartspik</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Chaenothecopsis nana</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>Tibell</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Stor-Gröningen S, Jmt</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>453168</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7031190</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Krokom</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Offerdal</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2023-02-25</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF19" t="inlineStr"/>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Johan Råghall</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 3433-2022 artfynd.xlsx
+++ b/artfynd/A 3433-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY19"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -773,6 +778,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018840</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018473</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018482</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018568</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018611</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018698</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018719</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018462</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018493</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1687,6 +1737,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018742</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1788,6 +1843,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018640</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1889,6 +1949,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018710</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1990,6 +2055,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018643</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2100,6 +2170,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018458</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2210,6 +2285,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018554</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2320,6 +2400,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018586</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2421,6 +2506,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018464</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2522,8 +2612,33 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107018496</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>